--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G8">

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G9">

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2102,22 +2102,22 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P11">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="Q11">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="R11">
         <v>2</v>
       </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
         <v>2.71</v>
@@ -2129,25 +2129,25 @@
         <v>1.34</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA11">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AB11">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC11">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="AD11">
         <v>1.19</v>
@@ -2156,10 +2156,10 @@
         <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG11">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="O13">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>5.04</v>
+        <v>4.8</v>
       </c>
       <c r="Q13">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="R13">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S13">
         <v>1.4</v>
@@ -2449,7 +2449,7 @@
         <v>2.62</v>
       </c>
       <c r="U13">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="V13">
         <v>1.33</v>
@@ -2461,25 +2461,25 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AA13">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="AD13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13">
         <v>2.1</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AK13">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="O14">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>6.05</v>
+        <v>5.25</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC14">
+        <v>1.94</v>
+      </c>
+      <c r="AD14">
         <v>1.82</v>
       </c>
-      <c r="AD14">
-        <v>1.85</v>
-      </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O11">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q11">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="R11">
         <v>2</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="U11">
         <v>2.92</v>
@@ -2129,7 +2129,7 @@
         <v>1.34</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2138,7 +2138,7 @@
         <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>2.83</v>
+        <v>3.06</v>
       </c>
       <c r="AA11">
         <v>2.12</v>
@@ -2437,10 +2437,10 @@
         <v>4.8</v>
       </c>
       <c r="Q13">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="R13">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
         <v>1.4</v>
@@ -2449,7 +2449,7 @@
         <v>2.62</v>
       </c>
       <c r="U13">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="V13">
         <v>1.33</v>
@@ -2461,19 +2461,19 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z13">
         <v>2.83</v>
       </c>
       <c r="AA13">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB13">
         <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AD13">
         <v>1.19</v>
@@ -2482,10 +2482,10 @@
         <v>1.03</v>
       </c>
       <c r="AF13">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG13">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK13">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,16 +2111,16 @@
         <v>2.6</v>
       </c>
       <c r="Q11">
-        <v>3.32</v>
+        <v>3.14</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S11">
         <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="U11">
         <v>2.92</v>
@@ -2129,7 +2129,7 @@
         <v>1.34</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2141,13 +2141,13 @@
         <v>3.06</v>
       </c>
       <c r="AA11">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AB11">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AD11">
         <v>1.19</v>
@@ -2175,7 +2175,7 @@
         <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>3.5</v>
       </c>
       <c r="P13">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="Q13">
         <v>2.16</v>
@@ -2443,10 +2443,10 @@
         <v>2.08</v>
       </c>
       <c r="S13">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T13">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U13">
         <v>3.16</v>
@@ -2455,25 +2455,25 @@
         <v>1.33</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>2.83</v>
+        <v>3.09</v>
       </c>
       <c r="AA13">
         <v>2.12</v>
       </c>
       <c r="AB13">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD13">
         <v>1.19</v>
@@ -2482,10 +2482,10 @@
         <v>1.03</v>
       </c>
       <c r="AF13">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2105,16 +2105,16 @@
         <v>2.5</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P11">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Q11">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S11">
         <v>1.4</v>
@@ -2126,7 +2126,7 @@
         <v>2.92</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
         <v>1.07</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O11">
         <v>3.18</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
         <v>1.43</v>
@@ -2434,22 +2434,22 @@
         <v>3.5</v>
       </c>
       <c r="P13">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q13">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U13">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="V13">
         <v>1.33</v>
@@ -2464,19 +2464,19 @@
         <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>3.09</v>
+        <v>2.81</v>
       </c>
       <c r="AA13">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AB13">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="AD13">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE13">
         <v>1.03</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK13">
         <v>2.3</v>
@@ -2597,22 +2597,22 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q14">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="S14">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T14">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="U14">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V14">
         <v>1.75</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z14">
         <v>6.35</v>
@@ -2633,13 +2633,13 @@
         <v>1.33</v>
       </c>
       <c r="AB14">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="AC14">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AD14">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AE14">
         <v>1.33</v>
@@ -2648,7 +2648,7 @@
         <v>1.44</v>
       </c>
       <c r="AG14">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="O10">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="P10">
         <v>3</v>
       </c>
       <c r="Q10">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R10">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T10">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U10">
-        <v>3.17</v>
+        <v>2.95</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z10">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA10">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AB10">
         <v>1.61</v>
       </c>
       <c r="AC10">
-        <v>3.85</v>
+        <v>4.12</v>
       </c>
       <c r="AD10">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE10">
         <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG10">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>3.25</v>
       </c>
       <c r="R11">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
         <v>1.4</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>3.5</v>
       </c>
       <c r="P13">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>2.21</v>
@@ -2482,10 +2482,10 @@
         <v>1.03</v>
       </c>
       <c r="AF13">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG13">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2606,7 +2606,7 @@
         <v>2.67</v>
       </c>
       <c r="S14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T14">
         <v>4.6</v>
@@ -2627,10 +2627,10 @@
         <v>1.11</v>
       </c>
       <c r="Z14">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="AA14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB14">
         <v>2.92</v>
@@ -2639,7 +2639,7 @@
         <v>1.88</v>
       </c>
       <c r="AD14">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AE14">
         <v>1.33</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -1948,55 +1948,55 @@
         <v>3</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="R10">
         <v>2.05</v>
       </c>
       <c r="S10">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="U10">
         <v>2.95</v>
       </c>
       <c r="V10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z10">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="AA10">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AB10">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC10">
-        <v>4.12</v>
+        <v>4.03</v>
       </c>
       <c r="AD10">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE10">
         <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O11">
         <v>3.18</v>
@@ -2111,22 +2111,22 @@
         <v>2.59</v>
       </c>
       <c r="Q11">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="U11">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="V11">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
         <v>1.07</v>
@@ -2135,22 +2135,22 @@
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z11">
         <v>3.06</v>
       </c>
       <c r="AA11">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AB11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC11">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD11">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
         <v>1.03</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,43 +2428,43 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
         <v>3.5</v>
       </c>
       <c r="P13">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q13">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="R13">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
         <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="U13">
         <v>3</v>
       </c>
       <c r="V13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W13">
         <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="Z13">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AA13">
         <v>2.14</v>
@@ -2476,13 +2476,13 @@
         <v>3.82</v>
       </c>
       <c r="AD13">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE13">
         <v>1.03</v>
       </c>
       <c r="AF13">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG13">
         <v>1.67</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
         <v>2.3</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2175,7 +2175,7 @@
         <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="U13">
         <v>3</v>
@@ -2464,7 +2464,7 @@
         <v>1.39</v>
       </c>
       <c r="Z13">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AA13">
         <v>2.14</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2105,10 +2105,10 @@
         <v>2.45</v>
       </c>
       <c r="O11">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -2446,7 +2446,7 @@
         <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="U13">
         <v>3</v>
@@ -2501,7 +2501,7 @@
         <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="O11">
         <v>3.5</v>
@@ -2111,49 +2111,49 @@
         <v>2.8</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T11">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="V11">
         <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="AA11">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB11">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD11">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
         <v>1.84</v>
@@ -2431,13 +2431,13 @@
         <v>1.61</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="Q13">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="R13">
         <v>2.1</v>
@@ -2458,13 +2458,13 @@
         <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z13">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AA13">
         <v>2.14</v>
@@ -2473,7 +2473,7 @@
         <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AD13">
         <v>1.22</v>
@@ -2485,7 +2485,7 @@
         <v>2.1</v>
       </c>
       <c r="AG13">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK13">
         <v>2.2</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1495,10 +1495,10 @@
         <v>0</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q10">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="R10">
         <v>2.05</v>
       </c>
       <c r="S10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T10">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="U10">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
         <v>1.37</v>
       </c>
       <c r="Z10">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="AA10">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="AB10">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC10">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
       <c r="AD10">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
         <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="O14">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="P14">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R14">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="S14">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
         <v>4.6</v>
       </c>
       <c r="U14">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V14">
         <v>1.75</v>
@@ -2624,31 +2624,31 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z14">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA14">
         <v>1.36</v>
       </c>
       <c r="AB14">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC14">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AD14">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF14">
         <v>1.44</v>
       </c>
       <c r="AG14">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC2">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD2">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
+        <v>1.7</v>
+      </c>
+      <c r="O3">
+        <v>3.9</v>
+      </c>
+      <c r="P3">
+        <v>3.75</v>
+      </c>
+      <c r="Q3">
+        <v>2.1</v>
+      </c>
+      <c r="R3">
+        <v>2.5</v>
+      </c>
+      <c r="S3">
+        <v>1.25</v>
+      </c>
+      <c r="T3">
+        <v>3.75</v>
+      </c>
+      <c r="U3">
+        <v>2.2</v>
+      </c>
+      <c r="V3">
+        <v>1.68</v>
+      </c>
+      <c r="W3">
+        <v>1.15</v>
+      </c>
+      <c r="X3">
+        <v>1.01</v>
+      </c>
+      <c r="Y3">
+        <v>1.1</v>
+      </c>
+      <c r="Z3">
+        <v>5.1</v>
+      </c>
+      <c r="AA3">
+        <v>1.49</v>
+      </c>
+      <c r="AB3">
+        <v>2.56</v>
+      </c>
+      <c r="AC3">
+        <v>2.15</v>
+      </c>
+      <c r="AD3">
+        <v>1.7</v>
+      </c>
+      <c r="AE3">
+        <v>1.27</v>
+      </c>
+      <c r="AF3">
+        <v>1.48</v>
+      </c>
+      <c r="AG3">
+        <v>2.36</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.15</v>
+      </c>
+      <c r="AK3">
         <v>2</v>
-      </c>
-      <c r="O3">
-        <v>3.4</v>
-      </c>
-      <c r="P3">
-        <v>3.2</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>1.7</v>
-      </c>
-      <c r="AB3">
-        <v>2</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="O4">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC4">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AD4">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="O5">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>6.25</v>
+        <v>3.7</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA5">
+        <v>1.63</v>
+      </c>
+      <c r="AB5">
+        <v>2.1</v>
+      </c>
+      <c r="AC5">
+        <v>2.59</v>
+      </c>
+      <c r="AD5">
+        <v>1.45</v>
+      </c>
+      <c r="AE5">
+        <v>1.17</v>
+      </c>
+      <c r="AF5">
         <v>1.6</v>
       </c>
-      <c r="AB5">
-        <v>2.2</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
+        <v>2.9</v>
+      </c>
+      <c r="O6">
+        <v>3.5</v>
+      </c>
+      <c r="P6">
+        <v>2.05</v>
+      </c>
+      <c r="Q6">
+        <v>3.66</v>
+      </c>
+      <c r="R6">
+        <v>2.3</v>
+      </c>
+      <c r="S6">
+        <v>1.29</v>
+      </c>
+      <c r="T6">
+        <v>3.5</v>
+      </c>
+      <c r="U6">
+        <v>2.32</v>
+      </c>
+      <c r="V6">
+        <v>1.59</v>
+      </c>
+      <c r="W6">
+        <v>1.11</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.16</v>
+      </c>
+      <c r="Z6">
+        <v>4.42</v>
+      </c>
+      <c r="AA6">
+        <v>1.63</v>
+      </c>
+      <c r="AB6">
+        <v>2.25</v>
+      </c>
+      <c r="AC6">
+        <v>2.45</v>
+      </c>
+      <c r="AD6">
+        <v>1.53</v>
+      </c>
+      <c r="AE6">
+        <v>1.18</v>
+      </c>
+      <c r="AF6">
+        <v>1.49</v>
+      </c>
+      <c r="AG6">
+        <v>2.39</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.67</v>
       </c>
-      <c r="O6">
-        <v>4</v>
-      </c>
-      <c r="P6">
-        <v>4.2</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>1.6</v>
-      </c>
-      <c r="AB6">
-        <v>2.15</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC7">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="AD7">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,65 +1613,65 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA8">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AB8">
+        <v>2.26</v>
+      </c>
+      <c r="AC8">
+        <v>2.44</v>
+      </c>
+      <c r="AD8">
+        <v>1.43</v>
+      </c>
+      <c r="AE8">
+        <v>1.18</v>
+      </c>
+      <c r="AF8">
+        <v>1.73</v>
+      </c>
+      <c r="AG8">
         <v>2</v>
       </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.57</v>
+        <v>2.19</v>
       </c>
       <c r="O9">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AA9">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB9">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,13 +1948,13 @@
         <v>2.87</v>
       </c>
       <c r="Q10">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="R10">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
         <v>2.55</v>
@@ -1969,34 +1969,34 @@
         <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.37</v>
       </c>
       <c r="Z10">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AA10">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AB10">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC10">
-        <v>4.1</v>
+        <v>4.02</v>
       </c>
       <c r="AD10">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
         <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>2.8</v>
       </c>
       <c r="Q11">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U11">
-        <v>2.87</v>
+        <v>3.22</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z11">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AA11">
         <v>2.07</v>
       </c>
       <c r="AB11">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC11">
-        <v>4.1</v>
+        <v>3.66</v>
       </c>
       <c r="AD11">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>1.61</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
         <v>5.2</v>
@@ -2446,7 +2446,7 @@
         <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="U13">
         <v>3</v>
@@ -2467,10 +2467,10 @@
         <v>3.1</v>
       </c>
       <c r="AA13">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB13">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC13">
         <v>4.1</v>
@@ -2479,7 +2479,7 @@
         <v>1.22</v>
       </c>
       <c r="AE13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
         <v>2.1</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
         <v>2.2</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="Q2">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="R2">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S2">
         <v>1.22</v>
       </c>
       <c r="T2">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="U2">
+        <v>2.15</v>
+      </c>
+      <c r="V2">
+        <v>1.65</v>
+      </c>
+      <c r="W2">
+        <v>1.17</v>
+      </c>
+      <c r="X2">
+        <v>1.02</v>
+      </c>
+      <c r="Y2">
+        <v>1.12</v>
+      </c>
+      <c r="Z2">
+        <v>4.65</v>
+      </c>
+      <c r="AA2">
+        <v>1.48</v>
+      </c>
+      <c r="AB2">
+        <v>2.45</v>
+      </c>
+      <c r="AC2">
         <v>2.2</v>
       </c>
-      <c r="V2">
+      <c r="AD2">
         <v>1.57</v>
       </c>
-      <c r="W2">
-        <v>1.14</v>
-      </c>
-      <c r="X2">
-        <v>1.01</v>
-      </c>
-      <c r="Y2">
-        <v>1.13</v>
-      </c>
-      <c r="Z2">
-        <v>4.8</v>
-      </c>
-      <c r="AA2">
-        <v>1.55</v>
-      </c>
-      <c r="AB2">
-        <v>2.42</v>
-      </c>
-      <c r="AC2">
-        <v>2.25</v>
-      </c>
-      <c r="AD2">
-        <v>1.62</v>
-      </c>
       <c r="AE2">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF2">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>2.53</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK2">
-        <v>1.73</v>
+        <v>3.06</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>3.66</v>
       </c>
       <c r="R3">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T3">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V3">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z3">
-        <v>5.1</v>
+        <v>4.42</v>
       </c>
       <c r="AA3">
+        <v>1.63</v>
+      </c>
+      <c r="AB3">
+        <v>2.25</v>
+      </c>
+      <c r="AC3">
+        <v>2.45</v>
+      </c>
+      <c r="AD3">
+        <v>1.53</v>
+      </c>
+      <c r="AE3">
+        <v>1.18</v>
+      </c>
+      <c r="AF3">
         <v>1.49</v>
       </c>
-      <c r="AB3">
-        <v>2.56</v>
-      </c>
-      <c r="AC3">
-        <v>2.15</v>
-      </c>
-      <c r="AD3">
-        <v>1.7</v>
-      </c>
-      <c r="AE3">
-        <v>1.27</v>
-      </c>
-      <c r="AF3">
-        <v>1.48</v>
-      </c>
       <c r="AG3">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="AK3">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q4">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="R4">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
+        <v>1.36</v>
+      </c>
+      <c r="T4">
+        <v>2.96</v>
+      </c>
+      <c r="U4">
+        <v>2.59</v>
+      </c>
+      <c r="V4">
+        <v>1.48</v>
+      </c>
+      <c r="W4">
+        <v>1.06</v>
+      </c>
+      <c r="X4">
+        <v>1.03</v>
+      </c>
+      <c r="Y4">
+        <v>1.26</v>
+      </c>
+      <c r="Z4">
+        <v>3.52</v>
+      </c>
+      <c r="AA4">
+        <v>1.87</v>
+      </c>
+      <c r="AB4">
+        <v>1.91</v>
+      </c>
+      <c r="AC4">
+        <v>2.98</v>
+      </c>
+      <c r="AD4">
+        <v>1.36</v>
+      </c>
+      <c r="AE4">
+        <v>1.08</v>
+      </c>
+      <c r="AF4">
+        <v>1.65</v>
+      </c>
+      <c r="AG4">
+        <v>2.07</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.22</v>
       </c>
-      <c r="T4">
-        <v>3.56</v>
-      </c>
-      <c r="U4">
-        <v>2.15</v>
-      </c>
-      <c r="V4">
-        <v>1.65</v>
-      </c>
-      <c r="W4">
-        <v>1.17</v>
-      </c>
-      <c r="X4">
-        <v>1.02</v>
-      </c>
-      <c r="Y4">
-        <v>1.12</v>
-      </c>
-      <c r="Z4">
-        <v>4.65</v>
-      </c>
-      <c r="AA4">
-        <v>1.48</v>
-      </c>
-      <c r="AB4">
-        <v>2.45</v>
-      </c>
-      <c r="AC4">
-        <v>2.2</v>
-      </c>
-      <c r="AD4">
-        <v>1.57</v>
-      </c>
-      <c r="AE4">
-        <v>1.21</v>
-      </c>
-      <c r="AF4">
-        <v>1.85</v>
-      </c>
-      <c r="AG4">
-        <v>1.85</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.05</v>
-      </c>
       <c r="AK4">
-        <v>3.06</v>
+        <v>1.67</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
+        <v>1.46</v>
+      </c>
+      <c r="O5">
+        <v>4.4</v>
+      </c>
+      <c r="P5">
+        <v>5.5</v>
+      </c>
+      <c r="Q5">
+        <v>1.91</v>
+      </c>
+      <c r="R5">
+        <v>2.4</v>
+      </c>
+      <c r="S5">
+        <v>1.29</v>
+      </c>
+      <c r="T5">
+        <v>3.3</v>
+      </c>
+      <c r="U5">
+        <v>2.34</v>
+      </c>
+      <c r="V5">
+        <v>1.58</v>
+      </c>
+      <c r="W5">
+        <v>1.11</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>1.14</v>
+      </c>
+      <c r="Z5">
+        <v>4.33</v>
+      </c>
+      <c r="AA5">
+        <v>1.59</v>
+      </c>
+      <c r="AB5">
+        <v>2.26</v>
+      </c>
+      <c r="AC5">
+        <v>2.44</v>
+      </c>
+      <c r="AD5">
+        <v>1.43</v>
+      </c>
+      <c r="AE5">
+        <v>1.18</v>
+      </c>
+      <c r="AF5">
         <v>1.73</v>
       </c>
-      <c r="O5">
-        <v>3.7</v>
-      </c>
-      <c r="P5">
-        <v>3.7</v>
-      </c>
-      <c r="Q5">
-        <v>2.25</v>
-      </c>
-      <c r="R5">
-        <v>2.38</v>
-      </c>
-      <c r="S5">
-        <v>1.24</v>
-      </c>
-      <c r="T5">
-        <v>3.38</v>
-      </c>
-      <c r="U5">
-        <v>2.39</v>
-      </c>
-      <c r="V5">
-        <v>1.53</v>
-      </c>
-      <c r="W5">
-        <v>1.13</v>
-      </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
-        <v>1.16</v>
-      </c>
-      <c r="Z5">
-        <v>4.15</v>
-      </c>
-      <c r="AA5">
-        <v>1.63</v>
-      </c>
-      <c r="AB5">
-        <v>2.1</v>
-      </c>
-      <c r="AC5">
-        <v>2.59</v>
-      </c>
-      <c r="AD5">
-        <v>1.45</v>
-      </c>
-      <c r="AE5">
-        <v>1.17</v>
-      </c>
-      <c r="AF5">
-        <v>1.6</v>
-      </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK5">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="O6">
         <v>3.5</v>
       </c>
       <c r="P6">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q6">
-        <v>3.66</v>
+        <v>2.92</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="U6">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="V6">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>4.42</v>
+        <v>3.91</v>
       </c>
       <c r="AA6">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB6">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AC6">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AD6">
+        <v>1.44</v>
+      </c>
+      <c r="AE6">
+        <v>1.13</v>
+      </c>
+      <c r="AF6">
+        <v>1.58</v>
+      </c>
+      <c r="AG6">
+        <v>2.19</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.22</v>
+      </c>
+      <c r="AK6">
         <v>1.53</v>
-      </c>
-      <c r="AE6">
-        <v>1.18</v>
-      </c>
-      <c r="AF6">
-        <v>1.49</v>
-      </c>
-      <c r="AG6">
-        <v>2.39</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.67</v>
-      </c>
-      <c r="AK6">
-        <v>1.33</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
+        <v>1.7</v>
+      </c>
+      <c r="O7">
+        <v>3.9</v>
+      </c>
+      <c r="P7">
+        <v>3.75</v>
+      </c>
+      <c r="Q7">
+        <v>2.1</v>
+      </c>
+      <c r="R7">
+        <v>2.5</v>
+      </c>
+      <c r="S7">
+        <v>1.25</v>
+      </c>
+      <c r="T7">
+        <v>3.75</v>
+      </c>
+      <c r="U7">
+        <v>2.2</v>
+      </c>
+      <c r="V7">
+        <v>1.68</v>
+      </c>
+      <c r="W7">
+        <v>1.15</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>1.1</v>
+      </c>
+      <c r="Z7">
+        <v>5.1</v>
+      </c>
+      <c r="AA7">
+        <v>1.49</v>
+      </c>
+      <c r="AB7">
+        <v>2.56</v>
+      </c>
+      <c r="AC7">
+        <v>2.15</v>
+      </c>
+      <c r="AD7">
+        <v>1.7</v>
+      </c>
+      <c r="AE7">
+        <v>1.27</v>
+      </c>
+      <c r="AF7">
+        <v>1.48</v>
+      </c>
+      <c r="AG7">
+        <v>2.36</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.15</v>
+      </c>
+      <c r="AK7">
         <v>2</v>
-      </c>
-      <c r="O7">
-        <v>3.4</v>
-      </c>
-      <c r="P7">
-        <v>3</v>
-      </c>
-      <c r="Q7">
-        <v>2.8</v>
-      </c>
-      <c r="R7">
-        <v>2.3</v>
-      </c>
-      <c r="S7">
-        <v>1.36</v>
-      </c>
-      <c r="T7">
-        <v>2.96</v>
-      </c>
-      <c r="U7">
-        <v>2.59</v>
-      </c>
-      <c r="V7">
-        <v>1.48</v>
-      </c>
-      <c r="W7">
-        <v>1.06</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.26</v>
-      </c>
-      <c r="Z7">
-        <v>3.52</v>
-      </c>
-      <c r="AA7">
-        <v>1.87</v>
-      </c>
-      <c r="AB7">
-        <v>1.91</v>
-      </c>
-      <c r="AC7">
-        <v>2.98</v>
-      </c>
-      <c r="AD7">
-        <v>1.36</v>
-      </c>
-      <c r="AE7">
-        <v>1.08</v>
-      </c>
-      <c r="AF7">
-        <v>1.65</v>
-      </c>
-      <c r="AG7">
-        <v>2.07</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.22</v>
-      </c>
-      <c r="AK7">
-        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q8">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="R8">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S8">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U8">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V8">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z8">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AA8">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AB8">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="AC8">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AD8">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF8">
+        <v>1.44</v>
+      </c>
+      <c r="AG8">
+        <v>2.53</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.25</v>
+      </c>
+      <c r="AK8">
         <v>1.73</v>
-      </c>
-      <c r="AG8">
-        <v>2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.04</v>
-      </c>
-      <c r="AK8">
-        <v>2.49</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="Q9">
-        <v>2.92</v>
+        <v>2.25</v>
       </c>
       <c r="R9">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="T9">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="U9">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="V9">
         <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>3.91</v>
+        <v>4.15</v>
       </c>
       <c r="AA9">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB9">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC9">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AD9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE9">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG9">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>3.66</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
         <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U3">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="V3">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z3">
-        <v>4.42</v>
+        <v>3.52</v>
       </c>
       <c r="AA3">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AB3">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AC3">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="AD3">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AG3">
-        <v>2.39</v>
+        <v>2.07</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
+        <v>1.22</v>
+      </c>
+      <c r="AK3">
         <v>1.67</v>
-      </c>
-      <c r="AK3">
-        <v>1.33</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G4">
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
+        <v>1.46</v>
+      </c>
+      <c r="O4">
+        <v>4.4</v>
+      </c>
+      <c r="P4">
+        <v>5.5</v>
+      </c>
+      <c r="Q4">
+        <v>1.91</v>
+      </c>
+      <c r="R4">
+        <v>2.4</v>
+      </c>
+      <c r="S4">
+        <v>1.29</v>
+      </c>
+      <c r="T4">
+        <v>3.3</v>
+      </c>
+      <c r="U4">
+        <v>2.34</v>
+      </c>
+      <c r="V4">
+        <v>1.58</v>
+      </c>
+      <c r="W4">
+        <v>1.11</v>
+      </c>
+      <c r="X4">
+        <v>1.01</v>
+      </c>
+      <c r="Y4">
+        <v>1.14</v>
+      </c>
+      <c r="Z4">
+        <v>4.33</v>
+      </c>
+      <c r="AA4">
+        <v>1.59</v>
+      </c>
+      <c r="AB4">
+        <v>2.26</v>
+      </c>
+      <c r="AC4">
+        <v>2.44</v>
+      </c>
+      <c r="AD4">
+        <v>1.43</v>
+      </c>
+      <c r="AE4">
+        <v>1.18</v>
+      </c>
+      <c r="AF4">
+        <v>1.73</v>
+      </c>
+      <c r="AG4">
         <v>2</v>
       </c>
-      <c r="O4">
-        <v>3.4</v>
-      </c>
-      <c r="P4">
-        <v>3</v>
-      </c>
-      <c r="Q4">
-        <v>2.8</v>
-      </c>
-      <c r="R4">
-        <v>2.3</v>
-      </c>
-      <c r="S4">
-        <v>1.36</v>
-      </c>
-      <c r="T4">
-        <v>2.96</v>
-      </c>
-      <c r="U4">
-        <v>2.59</v>
-      </c>
-      <c r="V4">
-        <v>1.48</v>
-      </c>
-      <c r="W4">
-        <v>1.06</v>
-      </c>
-      <c r="X4">
-        <v>1.03</v>
-      </c>
-      <c r="Y4">
-        <v>1.26</v>
-      </c>
-      <c r="Z4">
-        <v>3.52</v>
-      </c>
-      <c r="AA4">
-        <v>1.87</v>
-      </c>
-      <c r="AB4">
-        <v>1.91</v>
-      </c>
-      <c r="AC4">
-        <v>2.98</v>
-      </c>
-      <c r="AD4">
-        <v>1.36</v>
-      </c>
-      <c r="AE4">
-        <v>1.08</v>
-      </c>
-      <c r="AF4">
-        <v>1.65</v>
-      </c>
-      <c r="AG4">
-        <v>2.07</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK4">
-        <v>1.67</v>
+        <v>2.49</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="R5">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U5">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AA5">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AB5">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="AC5">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AD5">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF5">
+        <v>1.44</v>
+      </c>
+      <c r="AG5">
+        <v>2.53</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.25</v>
+      </c>
+      <c r="AK5">
         <v>1.73</v>
-      </c>
-      <c r="AG5">
-        <v>2</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.04</v>
-      </c>
-      <c r="AK5">
-        <v>2.49</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P6">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="Q6">
-        <v>2.92</v>
+        <v>2.25</v>
       </c>
       <c r="R6">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="T6">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="U6">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="V6">
         <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z6">
-        <v>3.91</v>
+        <v>4.15</v>
       </c>
       <c r="AA6">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AD6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q8">
-        <v>2.45</v>
+        <v>2.92</v>
       </c>
       <c r="R8">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S8">
+        <v>1.33</v>
+      </c>
+      <c r="T8">
+        <v>3.13</v>
+      </c>
+      <c r="U8">
+        <v>2.46</v>
+      </c>
+      <c r="V8">
+        <v>1.53</v>
+      </c>
+      <c r="W8">
+        <v>1.08</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1.21</v>
+      </c>
+      <c r="Z8">
+        <v>3.91</v>
+      </c>
+      <c r="AA8">
+        <v>1.75</v>
+      </c>
+      <c r="AB8">
+        <v>2.08</v>
+      </c>
+      <c r="AC8">
+        <v>2.7</v>
+      </c>
+      <c r="AD8">
+        <v>1.44</v>
+      </c>
+      <c r="AE8">
+        <v>1.13</v>
+      </c>
+      <c r="AF8">
+        <v>1.58</v>
+      </c>
+      <c r="AG8">
+        <v>2.19</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.22</v>
       </c>
-      <c r="T8">
-        <v>3.75</v>
-      </c>
-      <c r="U8">
-        <v>2.2</v>
-      </c>
-      <c r="V8">
-        <v>1.57</v>
-      </c>
-      <c r="W8">
-        <v>1.14</v>
-      </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>1.13</v>
-      </c>
-      <c r="Z8">
-        <v>4.8</v>
-      </c>
-      <c r="AA8">
-        <v>1.55</v>
-      </c>
-      <c r="AB8">
-        <v>2.42</v>
-      </c>
-      <c r="AC8">
-        <v>2.25</v>
-      </c>
-      <c r="AD8">
-        <v>1.62</v>
-      </c>
-      <c r="AE8">
-        <v>1.23</v>
-      </c>
-      <c r="AF8">
-        <v>1.44</v>
-      </c>
-      <c r="AG8">
-        <v>2.53</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.25</v>
-      </c>
       <c r="AK8">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>3.7</v>
+        <v>2.05</v>
       </c>
       <c r="Q9">
-        <v>2.25</v>
+        <v>3.66</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>4.15</v>
+        <v>4.42</v>
       </c>
       <c r="AA9">
         <v>1.63</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AD9">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AG9">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK9">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P11">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -2126,7 +2126,7 @@
         <v>3.22</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
         <v>1.07</v>
@@ -2431,7 +2431,7 @@
         <v>1.61</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
         <v>5.2</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -2612,10 +2612,10 @@
         <v>4.6</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="V14">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W14">
         <v>1.2</v>
@@ -2624,13 +2624,13 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z14">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA14">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB14">
         <v>3.1</v>
@@ -2639,16 +2639,16 @@
         <v>1.9</v>
       </c>
       <c r="AD14">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AE14">
         <v>1.36</v>
       </c>
       <c r="AF14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG14">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -638,16 +638,16 @@
         <v>1.3</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="P2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q2">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R2">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S2">
         <v>1.22</v>
@@ -677,7 +677,7 @@
         <v>1.48</v>
       </c>
       <c r="AB2">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AC2">
         <v>2.2</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK2">
         <v>3.06</v>
@@ -813,19 +813,19 @@
         <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
         <v>2.59</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
         <v>1.03</v>
@@ -871,7 +871,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="O4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q4">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R4">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S4">
         <v>1.29</v>
@@ -982,37 +982,37 @@
         <v>3.3</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="V4">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA4">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AB4">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AC4">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="AD4">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE4">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
         <v>1.73</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK4">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>2.32</v>
       </c>
       <c r="S5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U5">
         <v>2.2</v>
@@ -1181,7 +1181,7 @@
         <v>1.44</v>
       </c>
       <c r="AG5">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="O6">
         <v>3.7</v>
@@ -1296,55 +1296,55 @@
         <v>3.7</v>
       </c>
       <c r="Q6">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="R6">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T6">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="U6">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
         <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AA6">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC6">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AD6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="O7">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>3.75</v>
+        <v>2.09</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R7">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
         <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>5.1</v>
+        <v>4.32</v>
       </c>
       <c r="AA7">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AB7">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="AC7">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AD7">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AE7">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AF7">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AG7">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="AK7">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P8">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="Q8">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
-        <v>3.13</v>
+        <v>3.87</v>
       </c>
       <c r="U8">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="Z8">
-        <v>3.91</v>
+        <v>5.75</v>
       </c>
       <c r="AA8">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AB8">
-        <v>2.08</v>
+        <v>2.76</v>
       </c>
       <c r="AC8">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AD8">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AF8">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AG8">
-        <v>2.19</v>
+        <v>2.53</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK8">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="O9">
+        <v>3.74</v>
+      </c>
+      <c r="P9">
+        <v>2.8</v>
+      </c>
+      <c r="Q9">
+        <v>2.78</v>
+      </c>
+      <c r="R9">
+        <v>2.14</v>
+      </c>
+      <c r="S9">
+        <v>1.3</v>
+      </c>
+      <c r="T9">
+        <v>3.04</v>
+      </c>
+      <c r="U9">
+        <v>2.53</v>
+      </c>
+      <c r="V9">
+        <v>1.41</v>
+      </c>
+      <c r="W9">
+        <v>1.07</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.22</v>
+      </c>
+      <c r="Z9">
         <v>3.5</v>
       </c>
-      <c r="P9">
-        <v>2.05</v>
-      </c>
-      <c r="Q9">
-        <v>3.66</v>
-      </c>
-      <c r="R9">
-        <v>2.3</v>
-      </c>
-      <c r="S9">
-        <v>1.29</v>
-      </c>
-      <c r="T9">
-        <v>3.5</v>
-      </c>
-      <c r="U9">
-        <v>2.32</v>
-      </c>
-      <c r="V9">
-        <v>1.59</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
-        <v>1.16</v>
-      </c>
-      <c r="Z9">
-        <v>4.42</v>
-      </c>
       <c r="AA9">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AB9">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AC9">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="AD9">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AG9">
-        <v>2.39</v>
+        <v>2.09</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>3.1</v>
       </c>
       <c r="P10">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q10">
         <v>3.13</v>
@@ -1963,7 +1963,7 @@
         <v>2.9</v>
       </c>
       <c r="V10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
         <v>1.02</v>
@@ -1981,10 +1981,10 @@
         <v>2.21</v>
       </c>
       <c r="AB10">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC10">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="AD10">
         <v>1.24</v>
@@ -2123,7 +2123,7 @@
         <v>2.65</v>
       </c>
       <c r="U11">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="V11">
         <v>1.35</v>
@@ -2141,7 +2141,7 @@
         <v>3.08</v>
       </c>
       <c r="AA11">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
         <v>1.67</v>
@@ -2434,7 +2434,7 @@
         <v>3.7</v>
       </c>
       <c r="P13">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q13">
         <v>2.21</v>
@@ -2446,7 +2446,7 @@
         <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U13">
         <v>3</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P7">
-        <v>2.09</v>
+        <v>3.7</v>
       </c>
       <c r="Q7">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T7">
-        <v>3.5</v>
+        <v>3.87</v>
       </c>
       <c r="U7">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z7">
-        <v>4.32</v>
+        <v>5.75</v>
       </c>
       <c r="AA7">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AB7">
-        <v>2.22</v>
+        <v>2.76</v>
       </c>
       <c r="AC7">
-        <v>2.49</v>
+        <v>2.02</v>
       </c>
       <c r="AD7">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AE7">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AF7">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AG7">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="AK7">
-        <v>1.33</v>
+        <v>1.99</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="O8">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="P8">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q8">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="R8">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="S8">
+        <v>1.3</v>
+      </c>
+      <c r="T8">
+        <v>3.04</v>
+      </c>
+      <c r="U8">
+        <v>2.53</v>
+      </c>
+      <c r="V8">
+        <v>1.41</v>
+      </c>
+      <c r="W8">
+        <v>1.07</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
         <v>1.22</v>
       </c>
-      <c r="T8">
-        <v>3.87</v>
-      </c>
-      <c r="U8">
-        <v>2.1</v>
-      </c>
-      <c r="V8">
-        <v>1.75</v>
-      </c>
-      <c r="W8">
-        <v>1.18</v>
-      </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>1.07</v>
-      </c>
       <c r="Z8">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA8">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="AB8">
-        <v>2.76</v>
+        <v>1.99</v>
       </c>
       <c r="AC8">
-        <v>2.02</v>
+        <v>2.94</v>
       </c>
       <c r="AD8">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="AE8">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AG8">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
+        <v>2.9</v>
+      </c>
+      <c r="O9">
+        <v>3.5</v>
+      </c>
+      <c r="P9">
+        <v>2.09</v>
+      </c>
+      <c r="Q9">
+        <v>3.4</v>
+      </c>
+      <c r="R9">
+        <v>2.3</v>
+      </c>
+      <c r="S9">
+        <v>1.25</v>
+      </c>
+      <c r="T9">
+        <v>3.5</v>
+      </c>
+      <c r="U9">
+        <v>2.38</v>
+      </c>
+      <c r="V9">
+        <v>1.58</v>
+      </c>
+      <c r="W9">
+        <v>1.13</v>
+      </c>
+      <c r="X9">
+        <v>1.01</v>
+      </c>
+      <c r="Y9">
+        <v>1.17</v>
+      </c>
+      <c r="Z9">
+        <v>4.32</v>
+      </c>
+      <c r="AA9">
+        <v>1.65</v>
+      </c>
+      <c r="AB9">
+        <v>2.22</v>
+      </c>
+      <c r="AC9">
+        <v>2.49</v>
+      </c>
+      <c r="AD9">
+        <v>1.51</v>
+      </c>
+      <c r="AE9">
+        <v>1.17</v>
+      </c>
+      <c r="AF9">
+        <v>1.51</v>
+      </c>
+      <c r="AG9">
         <v>2.34</v>
       </c>
-      <c r="O9">
-        <v>3.74</v>
-      </c>
-      <c r="P9">
-        <v>2.8</v>
-      </c>
-      <c r="Q9">
-        <v>2.78</v>
-      </c>
-      <c r="R9">
-        <v>2.14</v>
-      </c>
-      <c r="S9">
-        <v>1.3</v>
-      </c>
-      <c r="T9">
-        <v>3.04</v>
-      </c>
-      <c r="U9">
-        <v>2.53</v>
-      </c>
-      <c r="V9">
-        <v>1.41</v>
-      </c>
-      <c r="W9">
-        <v>1.07</v>
-      </c>
-      <c r="X9">
-        <v>1</v>
-      </c>
-      <c r="Y9">
-        <v>1.22</v>
-      </c>
-      <c r="Z9">
-        <v>3.5</v>
-      </c>
-      <c r="AA9">
-        <v>1.78</v>
-      </c>
-      <c r="AB9">
-        <v>1.99</v>
-      </c>
-      <c r="AC9">
-        <v>2.94</v>
-      </c>
-      <c r="AD9">
-        <v>1.38</v>
-      </c>
-      <c r="AE9">
-        <v>1.1</v>
-      </c>
-      <c r="AF9">
-        <v>1.61</v>
-      </c>
-      <c r="AG9">
-        <v>2.09</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK9">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O10">
         <v>3.1</v>
       </c>
       <c r="P10">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q10">
-        <v>3.13</v>
+        <v>2.81</v>
       </c>
       <c r="R10">
         <v>2</v>
       </c>
       <c r="S10">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="U10">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z10">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AA10">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="AB10">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC10">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AD10">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF10">
+        <v>1.8</v>
+      </c>
+      <c r="AG10">
         <v>1.85</v>
       </c>
-      <c r="AG10">
-        <v>1.8</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T11">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="U11">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z11">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA11">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB11">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC11">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="AD11">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AG11">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK11">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="R13">
         <v>2.1</v>
@@ -2446,46 +2446,46 @@
         <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA13">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AB13">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AC13">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD13">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
         <v>2.2</v>

--- a/jogos_2026-10-01.xlsx
+++ b/jogos_2026-10-01.xlsx
@@ -612,36 +612,36 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="P2">
-        <v>8</v>
+        <v>7.53</v>
       </c>
       <c r="Q2">
         <v>1.67</v>
@@ -656,13 +656,13 @@
         <v>3.56</v>
       </c>
       <c r="U2">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="V2">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X2">
         <v>1.02</v>
@@ -674,10 +674,10 @@
         <v>4.65</v>
       </c>
       <c r="AA2">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AB2">
-        <v>2.49</v>
+        <v>2.04</v>
       </c>
       <c r="AC2">
         <v>2.2</v>
@@ -686,7 +686,7 @@
         <v>1.57</v>
       </c>
       <c r="AE2">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF2">
         <v>1.85</v>
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "90+4"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,130 +775,130 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="R3">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S3">
+        <v>1.34</v>
+      </c>
+      <c r="T3">
+        <v>3.08</v>
+      </c>
+      <c r="U3">
+        <v>2.51</v>
+      </c>
+      <c r="V3">
+        <v>1.51</v>
+      </c>
+      <c r="W3">
+        <v>1.08</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1.22</v>
+      </c>
+      <c r="Z3">
+        <v>3.81</v>
+      </c>
+      <c r="AA3">
+        <v>1.7</v>
+      </c>
+      <c r="AB3">
+        <v>1.99</v>
+      </c>
+      <c r="AC3">
+        <v>2.76</v>
+      </c>
+      <c r="AD3">
         <v>1.3</v>
       </c>
-      <c r="T3">
-        <v>3.2</v>
-      </c>
-      <c r="U3">
-        <v>2.59</v>
-      </c>
-      <c r="V3">
-        <v>1.44</v>
-      </c>
-      <c r="W3">
+      <c r="AE3">
         <v>1.1</v>
       </c>
-      <c r="X3">
-        <v>1.03</v>
-      </c>
-      <c r="Y3">
-        <v>1.26</v>
-      </c>
-      <c r="Z3">
-        <v>3.52</v>
-      </c>
-      <c r="AA3">
-        <v>1.87</v>
-      </c>
-      <c r="AB3">
-        <v>1.91</v>
-      </c>
-      <c r="AC3">
-        <v>2.98</v>
-      </c>
-      <c r="AD3">
-        <v>1.36</v>
-      </c>
-      <c r="AE3">
-        <v>1.08</v>
-      </c>
       <c r="AF3">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG3">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "90+4"]</t>
         </is>
       </c>
       <c r="AJ3">
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -957,20 +957,20 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="O4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q4">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R4">
         <v>2.45</v>
@@ -982,37 +982,37 @@
         <v>3.3</v>
       </c>
       <c r="U4">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="V4">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W4">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="AA4">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AB4">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AC4">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE4">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF4">
         <v>1.73</v>
@@ -1022,46 +1022,46 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>["20"]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ4">
+        <v>1.05</v>
+      </c>
+      <c r="AK4">
+        <v>2.46</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>2</v>
+      </c>
+      <c r="AN4">
+        <v>4</v>
+      </c>
+      <c r="AO4">
+        <v>10</v>
+      </c>
+      <c r="AP4">
+        <v>7</v>
+      </c>
+      <c r="AQ4">
+        <v>1.2</v>
+      </c>
+      <c r="AR4">
         <v>1.06</v>
       </c>
-      <c r="AK4">
-        <v>2.3</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-1</v>
-      </c>
-      <c r="AN4">
-        <v>-1</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>-1</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
       <c r="AS4">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,130 +1101,130 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="O5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q5">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="R5">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V5">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="W5">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB5">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AC5">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD5">
         <v>1.62</v>
       </c>
       <c r="AE5">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF5">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG5">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "90+4"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1255,139 +1255,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P6">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q6">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S6">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="T6">
-        <v>3.24</v>
+        <v>3.9</v>
       </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z6">
-        <v>4</v>
+        <v>6.05</v>
       </c>
       <c r="AA6">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AB6">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AC6">
-        <v>2.66</v>
+        <v>1.98</v>
       </c>
       <c r="AD6">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AF6">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AG6">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>["28", "90+1"]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1418,139 +1418,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="O7">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="R7">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="S7">
+        <v>1.3</v>
+      </c>
+      <c r="T7">
+        <v>3.04</v>
+      </c>
+      <c r="U7">
+        <v>2.53</v>
+      </c>
+      <c r="V7">
+        <v>1.44</v>
+      </c>
+      <c r="W7">
+        <v>1.07</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
         <v>1.22</v>
       </c>
-      <c r="T7">
-        <v>3.87</v>
-      </c>
-      <c r="U7">
-        <v>2.1</v>
-      </c>
-      <c r="V7">
-        <v>1.75</v>
-      </c>
-      <c r="W7">
-        <v>1.18</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>1.07</v>
-      </c>
       <c r="Z7">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA7">
+        <v>1.61</v>
+      </c>
+      <c r="AB7">
+        <v>1.73</v>
+      </c>
+      <c r="AC7">
+        <v>2.45</v>
+      </c>
+      <c r="AD7">
+        <v>1.25</v>
+      </c>
+      <c r="AE7">
+        <v>1.1</v>
+      </c>
+      <c r="AF7">
+        <v>1.61</v>
+      </c>
+      <c r="AG7">
+        <v>2.09</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>["67"]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>["37", "52"]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.25</v>
+      </c>
+      <c r="AK7">
         <v>1.43</v>
       </c>
-      <c r="AB7">
-        <v>2.76</v>
-      </c>
-      <c r="AC7">
-        <v>2.02</v>
-      </c>
-      <c r="AD7">
-        <v>1.79</v>
-      </c>
-      <c r="AE7">
-        <v>1.32</v>
-      </c>
-      <c r="AF7">
-        <v>1.42</v>
-      </c>
-      <c r="AG7">
-        <v>2.53</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.15</v>
-      </c>
-      <c r="AK7">
-        <v>1.99</v>
-      </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1581,139 +1581,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
+        <v>2.87</v>
+      </c>
+      <c r="O8">
+        <v>3.4</v>
+      </c>
+      <c r="P8">
+        <v>2.05</v>
+      </c>
+      <c r="Q8">
+        <v>3.29</v>
+      </c>
+      <c r="R8">
+        <v>2.19</v>
+      </c>
+      <c r="S8">
+        <v>1.25</v>
+      </c>
+      <c r="T8">
+        <v>3.4</v>
+      </c>
+      <c r="U8">
+        <v>2.38</v>
+      </c>
+      <c r="V8">
+        <v>1.58</v>
+      </c>
+      <c r="W8">
+        <v>1.12</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>1.17</v>
+      </c>
+      <c r="Z8">
+        <v>4.32</v>
+      </c>
+      <c r="AA8">
+        <v>1.48</v>
+      </c>
+      <c r="AB8">
+        <v>2.25</v>
+      </c>
+      <c r="AC8">
+        <v>2.49</v>
+      </c>
+      <c r="AD8">
+        <v>1.51</v>
+      </c>
+      <c r="AE8">
+        <v>1.17</v>
+      </c>
+      <c r="AF8">
+        <v>1.51</v>
+      </c>
+      <c r="AG8">
         <v>2.34</v>
       </c>
-      <c r="O8">
-        <v>3.74</v>
-      </c>
-      <c r="P8">
-        <v>2.8</v>
-      </c>
-      <c r="Q8">
-        <v>2.78</v>
-      </c>
-      <c r="R8">
-        <v>2.14</v>
-      </c>
-      <c r="S8">
-        <v>1.3</v>
-      </c>
-      <c r="T8">
-        <v>3.04</v>
-      </c>
-      <c r="U8">
-        <v>2.53</v>
-      </c>
-      <c r="V8">
-        <v>1.41</v>
-      </c>
-      <c r="W8">
-        <v>1.07</v>
-      </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8">
-        <v>1.22</v>
-      </c>
-      <c r="Z8">
-        <v>3.5</v>
-      </c>
-      <c r="AA8">
-        <v>1.78</v>
-      </c>
-      <c r="AB8">
-        <v>1.99</v>
-      </c>
-      <c r="AC8">
-        <v>2.94</v>
-      </c>
-      <c r="AD8">
-        <v>1.38</v>
-      </c>
-      <c r="AE8">
-        <v>1.1</v>
-      </c>
-      <c r="AF8">
-        <v>1.61</v>
-      </c>
-      <c r="AG8">
-        <v>2.09</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "72"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "51"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK8">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1744,16 +1744,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1765,118 +1765,118 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P9">
-        <v>2.09</v>
+        <v>4.33</v>
       </c>
       <c r="Q9">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="U9">
         <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>4.32</v>
+        <v>4.62</v>
       </c>
       <c r="AA9">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB9">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD9">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF9">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AG9">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>["49"]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
